--- a/rules/CORE-000099/negative/01/data/unit-test-coreid-CG0422-negative 1.xlsx
+++ b/rules/CORE-000099/negative/01/data/unit-test-coreid-CG0422-negative 1.xlsx
@@ -48,6 +48,10 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
     </font>
     <font>
@@ -64,13 +68,8 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -84,12 +83,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -130,10 +123,10 @@
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,18 +461,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -495,18 +488,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>vs.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>VS test data</v>
       </c>
     </row>
@@ -522,143 +515,143 @@
   <dimension ref="A1:F7"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Error group</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Sheet</v>
       </c>
-      <c r="C1" s="2" t="str">
+      <c r="C1" s="3" t="str">
         <v>Error level</v>
       </c>
-      <c r="D1" s="2" t="str">
+      <c r="D1" s="3" t="str">
         <v>Row num</v>
       </c>
-      <c r="E1" s="2" t="str">
+      <c r="E1" s="3" t="str">
         <v>Variable</v>
       </c>
-      <c r="F1" s="2" t="str">
+      <c r="F1" s="3" t="str">
         <v>Error value</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>vs.xpt</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="3" t="str">
         <v>Record</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="str">
+      <c r="E2" s="3" t="str">
         <v>VSTEST</v>
       </c>
-      <c r="F2" s="2" t="str">
+      <c r="F2" s="3" t="str">
         <v>Violation both VSORRES and VSSTAT populated</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" s="3" t="str">
         <v>vs.xpt</v>
       </c>
-      <c r="C3" s="2" t="str">
+      <c r="C3" s="3" t="str">
         <v>Record</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="str">
+      <c r="E3" s="3" t="str">
         <v>VSORRES</v>
       </c>
-      <c r="F3" s="2" t="str">
-        <v>SOMEVALUE</v>
+      <c r="F3" s="3" t="str">
+        <v>SOMEVALUE2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="str">
+      <c r="B4" s="3" t="str">
         <v>vs.xpt</v>
       </c>
-      <c r="C4" s="2" t="str">
+      <c r="C4" s="3" t="str">
         <v>Record</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>6</v>
       </c>
-      <c r="E4" s="2" t="str">
+      <c r="E4" s="3" t="str">
         <v>VSSTAT</v>
       </c>
-      <c r="F4" s="2" t="str">
-        <v>SOMEVALUE</v>
+      <c r="F4" s="3" t="str">
+        <v>SOMEVALUE3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="str">
+      <c r="B5" s="3" t="str">
         <v>vs.xpt</v>
       </c>
-      <c r="C5" s="2" t="str">
+      <c r="C5" s="3" t="str">
         <v>Record</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>5</v>
       </c>
-      <c r="E5" s="2" t="str">
+      <c r="E5" s="3" t="str">
         <v>VSTEST</v>
       </c>
-      <c r="F5" s="2" t="str">
+      <c r="F5" s="3" t="str">
         <v>Violation both VSORRES and VSSTAT populated</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="str">
+      <c r="B6" s="3" t="str">
         <v>vs.xpt</v>
       </c>
-      <c r="C6" s="2" t="str">
+      <c r="C6" s="3" t="str">
         <v>Record</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>5</v>
       </c>
-      <c r="E6" s="2" t="str">
+      <c r="E6" s="3" t="str">
         <v>VSORRES</v>
       </c>
-      <c r="F6" s="2" t="str">
+      <c r="F6" s="3" t="str">
         <v>123456789</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="2" t="str">
+      <c r="B7" s="3" t="str">
         <v>vs.xpt</v>
       </c>
-      <c r="C7" s="2" t="str">
+      <c r="C7" s="3" t="str">
         <v>Record</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>5</v>
       </c>
-      <c r="E7" s="2" t="str">
+      <c r="E7" s="3" t="str">
         <v>VSSTAT</v>
       </c>
-      <c r="F7" s="2" t="str">
-        <v>NOT DONE</v>
+      <c r="F7" s="3" t="str">
+        <v>SOMEVALUE1</v>
       </c>
     </row>
   </sheetData>
@@ -673,141 +666,141 @@
   <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>VSSEQ</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>VSTEST</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>VSORRES</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>VSSTAT</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="str">
+      <c r="A2" s="5" t="str">
         <v>Label for STUDYID</v>
       </c>
-      <c r="B2" s="4" t="str">
+      <c r="B2" s="5" t="str">
         <v>Label for DOMAIN</v>
       </c>
-      <c r="C2" s="4" t="str">
+      <c r="C2" s="5" t="str">
         <v>Label for USUBJID</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="5" t="str">
         <v>Label for VSSEQ</v>
       </c>
-      <c r="E2" s="4" t="str">
+      <c r="E2" s="5" t="str">
         <v>Label for VSTEST</v>
       </c>
-      <c r="F2" s="4" t="str">
+      <c r="F2" s="5" t="str">
         <v>Label for VSORRES</v>
       </c>
-      <c r="G2" s="4" t="str">
+      <c r="G2" s="5" t="str">
         <v>Label for VSSTAT</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="str">
+      <c r="A3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="B3" s="4" t="str">
+      <c r="B3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="C3" s="4" t="str">
+      <c r="C3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="D3" s="4" t="str">
+      <c r="D3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="E3" s="4" t="str">
+      <c r="E3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="F3" s="4" t="str">
+      <c r="F3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="G3" s="4" t="str">
+      <c r="G3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4">
+      <c r="A4" s="5">
         <v>40</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <v>40</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>40</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>8</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>40</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <v>40</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>40</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="str">
+      <c r="A5" s="3" t="str">
         <v>POCSTUDY</v>
       </c>
-      <c r="B5" s="2" t="str">
+      <c r="B5" s="3" t="str">
         <v>VS</v>
       </c>
-      <c r="C5" s="2" t="str">
+      <c r="C5" s="3" t="str">
         <v>POC-001</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="str">
+      <c r="E5" s="6" t="str">
         <v>Violation both VSORRES and VSSTAT populated</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>123456789</v>
       </c>
-      <c r="G5" s="6" t="str">
-        <v>NOT DONE</v>
+      <c r="G5" s="7" t="str">
+        <v>SOMEVALUE1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="str">
+      <c r="A6" s="3" t="str">
         <v>POCSTUDY</v>
       </c>
-      <c r="B6" s="2" t="str">
+      <c r="B6" s="3" t="str">
         <v>VS</v>
       </c>
-      <c r="C6" s="2" t="str">
+      <c r="C6" s="3" t="str">
         <v>POC-001</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>2</v>
       </c>
-      <c r="E6" s="7" t="str">
+      <c r="E6" s="6" t="str">
         <v>Violation both VSORRES and VSSTAT populated</v>
       </c>
-      <c r="F6" s="6" t="str">
-        <v>SOMEVALUE</v>
-      </c>
-      <c r="G6" s="6" t="str">
-        <v>SOMEVALUE</v>
+      <c r="F6" s="7" t="str">
+        <v>SOMEVALUE2</v>
+      </c>
+      <c r="G6" s="7" t="str">
+        <v>SOMEVALUE3</v>
       </c>
     </row>
   </sheetData>
